--- a/materials/预实验2被试方案.xlsx
+++ b/materials/预实验2被试方案.xlsx
@@ -1,46 +1,483 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\experiment6\materials\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDF8BF1-4DF7-4C40-A43A-6A63CC97B287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="被试方案" sheetId="1" r:id="rId1"/>
+    <sheet name="预实验被试方案" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="141">
+  <si>
+    <t>被试编号</t>
+  </si>
+  <si>
+    <t>被试姓名</t>
+  </si>
+  <si>
+    <t>核心创意点与设定</t>
+  </si>
+  <si>
+    <t>高光画面描述</t>
+  </si>
+  <si>
+    <t>主打广告语</t>
+  </si>
+  <si>
+    <t>提交时间</t>
+  </si>
+  <si>
+    <t>是否自动保存</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>王锦</t>
+  </si>
+  <si>
+    <t>或许可以和功夫熊猫等动画形象联名，打造一个“独眼苹果侠”，他曾经是江湖上最强的一代武林宗师，但因患有残疾、容颜老去而隐退江湖，被人遗忘，但其实武功功底仍在。</t>
+  </si>
+  <si>
+    <t>昏暗的铁匠铺里，退隐的苹果大师正在修些什么东西，光柱照射，聚焦苹果大师一人，空气中悬浮着铁匠粉末，凑近看才发现苹果大师的匠心独运，在雕刻年轻时的武林大像。</t>
+  </si>
+  <si>
+    <t>伤疤越深，武功越狠。</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:10:18</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>彭超强</t>
+  </si>
+  <si>
+    <t>在超市的便宜苹果区，那些被嫌弃的丑苹果的。他们觉得子的空有高糖且没有人来观看问道，直到苏打水的出现才让他们自己丑苹果内心发散出来让全世界观看</t>
+  </si>
+  <si>
+    <t>高光时刻就是一个一个的丑苹果丢到榨汁机里面打成水，榨出汁水，拧开瓶盖气泡滋滋冒泡看的有人喝了一小口，看那个小眼睛都亮了。</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:12:22</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>郭旭</t>
+  </si>
+  <si>
+    <t>故事发生在果园，主角是果园的主人。他在卖果子的时候，发现很多品相差的苹果都被扔在地上，他觉得很可惜，随手捡起一个吃了一口。觉得很甜，接着把这些苹果榨成了苏打水，原本被人淘汰的苹果变成了一款时尚的苏打水，吸引人们纷纷购买。</t>
+  </si>
+  <si>
+    <t>给丑苹果加一些细节特写，画面色彩更加暗淡，与之前高品质的苹果形成对比，给人们带来视觉上的冲击，突出丑苹果被人嫌弃的画面。</t>
+  </si>
+  <si>
+    <t>丑苹果</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:14:34</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>杨紫梅</t>
+  </si>
+  <si>
+    <t>故事发生在一个果园里，周围都是长得很好的果子，而这是一个有损伤的果子，在产品中是主要的人物，它走在路上遍体鳞伤的感觉，但是还是坚持不懈，不管身后如何。走着走着经过一段强烈的光，然后前面有一个滑滑梯，从滑滑梯滑下来，变成饮料。</t>
+  </si>
+  <si>
+    <t>虽然有难看的外表，脱下外皮后是干干净净的身体，如何从滑滑梯下来是一瓶饮料，饮料很有特色，透过瓶身可以清楚看到来历。</t>
+  </si>
+  <si>
+    <t>饱经风霜初心仍在。</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:14:39</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>张语庭</t>
+  </si>
+  <si>
+    <t>故事发生在香坊招牌，一堆不被相貌所定义的女孩儿们聚在一起，她们马上就要去拯救江湖，直面敌人，临走前，将士们递给女孩儿们一打“丑苹果”苏打水，喝下后，无所畏惧，勇敢做自己！</t>
+  </si>
+  <si>
+    <t>当包装初次亮相的时候，它的晶莹剔透吸引了无数人。雀斑般的苹果与地面碰撞的一瞬间迸发了光亮，阳光貌似形成了一道分割线，暗处的也在其衬托下闪闪发光。盖子拧开的瞬间，味道沁人心脾，争先恐后涌出的气泡。</t>
+  </si>
+  <si>
+    <t>受伤的苹果带你走出偏见</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:15:32</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>王明珠</t>
+  </si>
+  <si>
+    <t>故事发生在超市里，那些有伤疤、长得歪的丑苹果被人嫌弃，只能待在角落。大家都嫌它们丑，没人要，只能扔在角落。结果把它们做成苏打水，一喝才发现，比那些好看的苹果还甜还香，一下子就改变了大家以貌取果的想法</t>
+  </si>
+  <si>
+    <t>先拍丑苹果被丢在一边，然后被放进榨汁机，咔嚓一声榨出金黄的果汁，气泡在杯子里冒。有人喝了一口，眼睛一下就亮了，嘴角忍不住往上扬，表情特别惊喜，暖黄的光打在他脸上，看着特别治愈</t>
+  </si>
+  <si>
+    <t>别光看外表，丑苹果也能甜到你心里</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:15:35</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>雷文杰</t>
+  </si>
+  <si>
+    <t>故事发生在遥远而神秘的火星，这里从来没有生物的遗迹，我是一名来自地球的宇航员，在这似乎不可能的世界，我靠着本公司生产的呼吸机生存了下来。</t>
+  </si>
+  <si>
+    <t>沙尘暴突然来袭，我摔倒在地，呼吸困难。胸前的呼吸机亮起蓝光，"滴"一声启动，清新空气涌入。我大口喘气，金色阳光穿透风沙，照在闪烁的机器上，像一颗蓝色的心脏在跳动。</t>
+  </si>
+  <si>
+    <t>呼吸机，在火星你也能尽情BREATH</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:15:57</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>场景：水果评选，评分第一可以得到推广
+角色：丑苹果
+故事线:通过独特的口味得到大众的认可，获得评分第一，被大众熟悉</t>
+  </si>
+  <si>
+    <t>丑苹果因外貌被人嫌弃，被其他水果排挤在外，但凭借自己独有的口味说服众人，从而登上评分榜座位，伤痕</t>
+  </si>
+  <si>
+    <t>纯天然无添加，都是我的独特风格</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:18:01</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>钟儒雅</t>
+  </si>
+  <si>
+    <t>故事发生在农场，有两个水果，一个是丑果，另一个是完美的果子，上帝要挑选一个全世界最甜的果子，选择了其貌不扬的丑果</t>
+  </si>
+  <si>
+    <t>丑果表皮粗糙，左侧有一个深褐色的凹陷（那是冰雹留下的旧伤），像是一道愈合后的伤疤。在周围一群光鲜亮丽的"模特苹果"中间，它显得格格不入，像是个混入贵族舞会的乞丐，局促、丑陋、甚至带着泥土的狼狈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上帝闻到了它的甜，所以忍不住多咬了一口。
+不完美是最大的完美
+</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:33:09</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>晓晓</t>
+  </si>
+  <si>
+    <t>场景：奇幻动画里面的苹果人物，每一个苹果都要进行游戏才可以成为完美外观果。
+角色：有两个苹果通过游戏决定是否是完美外观果。
+故事核心：苹果经过游戏被打败成丑苹果，最后选择了完美外观果，可是在生产的过程中发现味道并不是这样。</t>
+  </si>
+  <si>
+    <t>用暖色调，左边是苹果一号，另外一个是苹果二号，通过对游戏的竞争，谁赢了比赛就乐意成为完美外观果。一场场比赛下来，清脆的苹果咔咔的搏斗，苹果汁水的美味弥漫在比赛场地，就在这一刻时，苹果一号战胜了苹果二号，成为了完美外观果</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:33:11</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>叶琳</t>
+  </si>
+  <si>
+    <t>在一个“颜值即正义“的苹果世界里，长得丑、有伤疤的苹果全被当成次品，要送去当饲料。主角就是这样一只丑苹果，它发现自己的伤疤里藏着更甜的味道。丑苹果苏打水把它的伤疤履历印在瓶身上，告诉大家：别光看脸，不完美的外表下，藏着更棒的甜。</t>
+  </si>
+  <si>
+    <t>满是伤疤的丑苹果被丢进次品筐，镜头拉近，琥珀色的糖液从疤痕里渗出来，像小泪珠在果皮上滚，暖光一照，被炸成汁。</t>
+  </si>
+  <si>
+    <t>伤疤里的甜，才是真的</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:35:37</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>黄芷璐</t>
+  </si>
+  <si>
+    <t>次级果的奇幻穿越。次级果穿越多条世界线，条条时间线无一例外次级果都是被遗弃的命运；而有条时间线不一样，是一个以丑为美的世界，次级果因为外表而被包裹上华美的外衣和金银珠宝在展厅展示，次级果感受到了欢迎和喜悦，但是它觉得不对，本应该是自己的伤痕铸就了自己的甜度，可无人在意内涵。次级果离开了，只带着一张写着来历的纸。最后它来到了一个工厂，它看见果子不分好坏，只看内在，而它的内在因伤痕而熠熠生辉，它选择留下。它大受欢迎。</t>
+  </si>
+  <si>
+    <t>在以丑为美的世界，次级果感受到了欢迎和喜悦，它感觉自己从未被如此重视过。但是它觉得不对，本应该是自己的伤痕铸就了自己的甜度，可无人在意内涵。次级果再三犹豫，最终在华丽背景的衬托下默默离开了，只带着一张写着来历的纸。</t>
+  </si>
+  <si>
+    <t>甜来自我的伤痕。</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:50:47</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>商知源</t>
+  </si>
+  <si>
+    <t>发生在苹果园，把苹果都拟人化一些，丑陋且残缺的苹果们一直都很自卑，一直被完美无缺的苹果们嘲笑，但是有一天科学家们突然发现了丑苹果的美，然后他们开始被人们看到重视</t>
+  </si>
+  <si>
+    <t>完美漂亮的苹果与丑苹果还有精致的包装与粗糙的标签都出现在同一画面，但把光束聚焦在丑苹果和粗糙的标签上，然后画面一转是人们尝过这款饮料后的赞美</t>
+  </si>
+  <si>
+    <t>不完美本身也是一种美</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:50:55</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>韩烨</t>
+  </si>
+  <si>
+    <t>故事发生在武侠世界，每个苏打水都在宗门里有排名。主角是带有伤疤的蒙面自卑小苏打水，前期因为脸上的伤疤一直被宗门排挤，他虽自卑却没有堕落放弃，自己会在月黑风高的夜晚练习拳法。但是武侠世界后期接入了实验室系统，跟科技接轨，每个人的潜活因子（内在甜度）都被展现，结果就是伤疤苏打水的等级排的很高，大家包括他自己也终于意识到他的伤疤是厚积薄发的体现。</t>
+  </si>
+  <si>
+    <t>最高光画面是被揭晓潜活因子（内在甜度）时，每个人震撼的表情，暖光打在主角头上，四周的人都是蒙太奇效果旋转，背景音乐由紧张激烈到激动，主角抬起带有伤疤的脸，切特写·，脸上有冷艳的光。</t>
+  </si>
+  <si>
+    <t>你们都不看好我，偏偏是我。丑苹果苏打水，喝出你的态度。</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:51:25</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>孙婉馨</t>
+  </si>
+  <si>
+    <t>我会把场景设定为农民伯伯一个一个摘下树上的丑苹果，或者捡起地上的烂苹果，然后把苹果旋转180度，变成气泡特效，展示出设计的苏打水瓶身和宣传语，一大帮年轻人穿着潮流，戴耳机，滑滑板，互相撞瓶喝苏打水，再转场会到农民伯伯也聚瓶喝苏打水，互相点头，带着微笑，表明产品没有滞销，甚至被更好地销售出去了。</t>
+  </si>
+  <si>
+    <t>丑吗？丑的才甜！</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:54:55</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>肖金花</t>
+  </si>
+  <si>
+    <t>主角是丑苹果形象的娃娃。在堆满精致商品的超市里，一只顶着日晒斑的丑苹果娃娃钻进了冷柜中苏打水的瓶身，被偶然逛到这的顾客发现，好奇心驱使他拿起来看了看。</t>
+  </si>
+  <si>
+    <t>原本只是一瓶毫不起眼的苏打水因为丑苹果娃娃形象的结合这会显得非常的与众不同。</t>
+  </si>
+  <si>
+    <t>一口见真心。</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:55:01</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>李炫</t>
+  </si>
+  <si>
+    <t>在农民伯伯果园里面，每一个水果都努力生长着，他们等待着自己长大，被挑选成为更好的果子而奋斗着。就连苹果这一款被戏称为“充满着性缩力”的水果，也毫不例外。
+角色：一个又小又凹凸不平的苹果，主人公
+它成长的故事：从被取笑到自我怀疑再到被挑选的惊喜和释然</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+在经历了其他苹果的取笑之后，小丑苹果他没有放弃自己去努力的生长，尽管自己身上有很多的伤痕和凹凸不平，他仍然去努力的身上，无论是刮风还是下雨。最后他终于在一个春天，但他苏醒的时候，农民伯伯把它从枝桠上摘下来了，它也从睡梦中迎来了属于自己的春天。
+</t>
+  </si>
+  <si>
+    <t>丑苹果苏打水，值得更好的品味</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:56:57</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>李欣欣</t>
+  </si>
+  <si>
+    <t>在一个果园里，果农正在采摘苹果，但是今年的收成不尽人意，土地上很多被市场淘汰的次级果。果农很失望，随手捡起地上的苹果吃了一口，他感觉非常甜。突然来了灵感，想到因为外表被淘汰的苹果，把它们榨成苏打水就能让消费者接受了。</t>
+  </si>
+  <si>
+    <t>画面描述了果农在采摘苹果，因为收成不好，非常失落。吃了一口丑苹果，豁然开朗，做出了“丑苹果”苏打水，然后画面从暗淡色转为明亮和鲜艳的色彩。</t>
+  </si>
+  <si>
+    <t>原料和成品的极致反转，丑苹果苏打水。</t>
+  </si>
+  <si>
+    <t>2026-02-23 02:57:47</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>高睿儿</t>
+  </si>
+  <si>
+    <t>丑苹果来到了疯狂水果城，被长的圆滚滚的胖果嘲笑，两果开战，丑苹果受了伤流了汁液，才被发现原来他的糖度极高</t>
+  </si>
+  <si>
+    <t>丑苹果受了伤，镜头特写向他的伤口，伤口分泌出糖分和此生代谢物，由于纯度很高发着光，照的周围的水果睁不开眼</t>
+  </si>
+  <si>
+    <t>小小丑苹果蕴含大大的能量</t>
+  </si>
+  <si>
+    <t>2026-02-23 03:03:04</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>徐毓</t>
+  </si>
+  <si>
+    <t>以丑苹果味主角，讲述它的外表受到了市场的抛弃，却在自愈的过程中孕育了更加不一样的故事，核心反转，不完美的外面却是整体风味的来源</t>
+  </si>
+  <si>
+    <t>2026-02-23 03:31:58</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>陈浩朋</t>
+  </si>
+  <si>
+    <t>“丑苹果”的逆袭之路，你是丑苹果，从小就不被人看好，因为自己不符合世俗的审美，不被人们接受，可是在你自身特质的优异，你终于被人们发现并且珍视，开启了独属于自己的逆袭之路。</t>
+  </si>
+  <si>
+    <t>那是一个长着翅膀的的实验室，他发现了你的闪耀点，你优异的糖分含量，深入人们内心，完全是甜心使者，让人明白了看人不能只看外表，苹果也是。就这样，你被制作成了苏打水，完成了自己的逆袭之路，让那些看不起你的人和苹果啪啪打脸。</t>
+  </si>
+  <si>
+    <t>主打原果榨取的丑苹果苏打水，让你享受甜蜜至极的口味，让每一个丑苹果都得到新生！人们不能只看外表不看内心，苹果也是。</t>
+  </si>
+  <si>
+    <t>2026-02-23 03:58:45</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>王婧</t>
+  </si>
+  <si>
+    <t>一个充满怀旧氛围的场景下，一颗苹果被丢进了垃圾桶。随后又被捡了起来，被人发掘出它的内在价值。
+产品是主要角色，贯穿整个广告</t>
+  </si>
+  <si>
+    <t>苹果表皮炸裂开，让人感觉有很多汁水很甜的样子。苹果被制作成饮品，男女老少都能喝，同时传递健康的理念。</t>
+  </si>
+  <si>
+    <t>不完美，还更甜。</t>
+  </si>
+  <si>
+    <t>2026-02-23 04:08:53</t>
+  </si>
+  <si>
+    <t>在农民伯伯收烂苹果的时候放比较平和舒缓，稍微有一点小哀伤的的音乐，再转场时放动感的音乐，展示年轻人的活力，再转场再转场回到农民伯伯那边的场景时可以放比较俏皮一点的音乐，细致拍摄农民伯伯脸上有着汗珠喝苏打水这样的近景。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平庸的苹果，反转的味道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>别看我长的丑和磕碜，我其实内心很甜，不要被我的外迷惑了，我的甜度可是完美苹果的1.5倍，现在我变成苏打气泡水，没喝一口都是美味的味道。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特写一颗贴着战损标签的丑苹果，苹果本身带着斑驳的斑点，然后被放入了榨汁机，气泡汁液注入再生纸瓶身。拧开瓶盖，气泡带着清香浮现了，字幕有几个字，不完美，才是自然的本味</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不完美，才是自然的本味</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -64,14 +501,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,35 +844,550 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="5" width="34.83203125" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>被试编号</v>
-      </c>
-      <c r="B1" t="str">
-        <v>被试姓名</v>
-      </c>
-      <c r="C1" t="str">
-        <v>核心创意点与设定</v>
-      </c>
-      <c r="D1" t="str">
-        <v>高光画面描述</v>
-      </c>
-      <c r="E1" t="str">
-        <v>主打广告语</v>
-      </c>
-      <c r="F1" t="str">
-        <v>提交时间</v>
-      </c>
-      <c r="G1" t="str">
-        <v>是否自动保存</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F7" t="s">
+        <v>129</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="135" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" t="s">
+        <v>72</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="195" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="165" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="150" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F23" t="s">
+        <v>135</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G23">
+    <sortCondition ref="A2:A23"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/materials/预实验2被试方案.xlsx
+++ b/materials/预实验2被试方案.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\experiment6\materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDF8BF1-4DF7-4C40-A43A-6A63CC97B287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81167278-73C2-4667-B9D4-699E622A073C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
